--- a/test.xlsx
+++ b/test.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -18,8 +18,16 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>dededefrfr</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -111,7 +119,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -146,7 +154,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -323,7 +331,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -332,8 +340,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test.xlsx
+++ b/test.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projet informatique\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A3D4AC-6FFD-4B71-81C5-EE935094227D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -14,20 +20,26 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>dededefrfr</t>
   </si>
+  <si>
+    <t>sedededede</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -331,20 +343,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projet informatique\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A3D4AC-6FFD-4B71-81C5-EE935094227D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -28,18 +22,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>dededefrfr</t>
   </si>
   <si>
     <t>sedededede</t>
   </si>
+  <si>
+    <t>vfvfvfvf</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -343,25 +340,30 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
